--- a/performance_tracking_forms/010_performance_analytics_support_request_form--performance_tracking_forms.xlsx
+++ b/performance_tracking_forms/010_performance_analytics_support_request_form--performance_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'tool_1',_'label':_'tool_1'}</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'tool_1', 'label': 'tool_1'}</t>
+          <t>tool 1</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tool_2',_'label':_'tool_2'}</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'tool_2', 'label': 'tool_2'}</t>
+          <t>tool 2</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'tool_3',_'label':_'tool_3'}</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'tool_3', 'label': 'tool_3'}</t>
+          <t>tool 3</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'version_1',_'label':_'version_1'}</t>
+          <t>version_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'version_1', 'label': 'version_1'}</t>
+          <t>version 1</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'version_2',_'label':_'version_2'}</t>
+          <t>version_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'version_2', 'label': 'version_2'}</t>
+          <t>version 2</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'data_source_1',_'label':_'data_source_1'}</t>
+          <t>data_source_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'data_source_1', 'label': 'data_source_1'}</t>
+          <t>data source 1</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'data_source_2',_'label':_'data_source_2'}</t>
+          <t>data_source_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'data_source_2', 'label': 'data_source_2'}</t>
+          <t>data source 2</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'data_source_3',_'label':_'data_source_3'}</t>
+          <t>data_source_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'data_source_3', 'label': 'data_source_3'}</t>
+          <t>data source 3</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'time_of_day_1',_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'time_of_day_1', 'label': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'time_of_day_2',_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'time_of_day_2', 'label': 'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'time_of_day_3',_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'time_of_day_3', 'label': 'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'priority_1',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'priority_1', 'label': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'priority_2',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'priority_2', 'label': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'priority_3',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'priority_3', 'label': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'urgency_1',_'label':_'urgent'}</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'urgency_1', 'label': 'urgent'}</t>
+          <t>urgent</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'urgency_2',_'label':_'not_urgent'}</t>
+          <t>not_urgent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'urgency_2', 'label': 'not_urgent'}</t>
+          <t>not urgent</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'urgency_3',_'label':_'sometime_in_a_week'}</t>
+          <t>sometime_in_a_week</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'urgency_3', 'label': 'sometime_in_a_week'}</t>
+          <t>sometime in a week</t>
         </is>
       </c>
     </row>
